--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF74AB6-12D1-A141-9D9E-F5E4B9ADE5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5A7EFE-52B6-C541-96AD-5437A1F80B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
   <si>
     <t>key</t>
   </si>
@@ -207,6 +207,24 @@
   </si>
   <si>
     <t>cc-by-sa-4.0</t>
+  </si>
+  <si>
+    <t>Rhys</t>
+  </si>
+  <si>
+    <t>Manners</t>
+  </si>
+  <si>
+    <t>Hyacinthe</t>
+  </si>
+  <si>
+    <t>Nyirahabimana</t>
+  </si>
+  <si>
+    <t>International Institute of Tropical Agriculture</t>
+  </si>
+  <si>
+    <t>0000-0003-0213-5462</t>
   </si>
 </sst>
 </file>
@@ -707,7 +725,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -775,21 +793,52 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
       </c>
       <c r="E4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
         <v>50</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F6" t="s">
         <v>49</v>
       </c>
     </row>
@@ -806,6 +855,7 @@
     <col min="1" max="1" width="38.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="59.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -824,35 +874,35 @@
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{DBD07CB8-4C60-DC49-A47F-A5C36097E2A4}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{DBD07CB8-4C60-DC49-A47F-A5C36097E2A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5A7EFE-52B6-C541-96AD-5437A1F80B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
